--- a/healthcare_forms/004_palliative_care_monitoring_form--healthcare_forms.xlsx
+++ b/healthcare_forms/004_palliative_care_monitoring_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'mild'}</t>
+          <t>mild</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Mild'}</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'moderate'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'severe'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Severe'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'improved'}</t>
+          <t>improved</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Improved'}</t>
+          <t>Improved</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'stable'}</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Stable'}</t>
+          <t>Stable</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'decreased'}</t>
+          <t>decreased</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Decreased'}</t>
+          <t>Decreased</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'discharged'}</t>
+          <t>discharged</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Discharged'}</t>
+          <t>Discharged</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'not_discharged'}</t>
+          <t>not_discharged</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Not Discharged'}</t>
+          <t>Not Discharged</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'nurse'}</t>
+          <t>nurse</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Nurse'}</t>
+          <t>Nurse</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'therapist'}</t>
+          <t>therapist</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Therapist'}</t>
+          <t>Therapist</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'admitted'}</t>
+          <t>admitted</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Admitted'}</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'discharged'}</t>
+          <t>discharged</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Discharged'}</t>
+          <t>Discharged</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'unknown'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Unknown'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Yes'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'No'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'cardiology'}</t>
+          <t>cardiology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Cardiology'}</t>
+          <t>Cardiology</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'oncology'}</t>
+          <t>oncology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Oncology'}</t>
+          <t>Oncology</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'pulmonology'}</t>
+          <t>pulmonology</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Pulmonology'}</t>
+          <t>Pulmonology</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'palliative_care'}</t>
+          <t>palliative_care</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Palliative Care'}</t>
+          <t>Palliative Care</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'hospice_care'}</t>
+          <t>hospice_care</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Hospice Care'}</t>
+          <t>Hospice Care</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'dermatology'}</t>
+          <t>dermatology</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Dermatology'}</t>
+          <t>Dermatology</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'cardiology'}</t>
+          <t>cardiology</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Cardiology'}</t>
+          <t>Cardiology</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'neurology'}</t>
+          <t>neurology</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Neurology'}</t>
+          <t>Neurology</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'improved'}</t>
+          <t>improved</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Improved'}</t>
+          <t>Improved</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'stable'}</t>
+          <t>stable</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Stable'}</t>
+          <t>Stable</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'decreased'}</t>
+          <t>decreased</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Decreased'}</t>
+          <t>Decreased</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'nurse'}</t>
+          <t>nurse</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Nurse'}</t>
+          <t>Nurse</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'therapist'}</t>
+          <t>therapist</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Therapist'}</t>
+          <t>Therapist</t>
         </is>
       </c>
     </row>
